--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run8/epoch_70/per_file_predictions_epoch_70.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run8/epoch_70/per_file_predictions_epoch_70.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="497">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="490">
   <si>
     <t>Filename</t>
   </si>
@@ -808,703 +808,682 @@
     <t>0,1,1,0</t>
   </si>
   <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.9946,0.0010,0.0010,0.0003</t>
-  </si>
-  <si>
-    <t>0.0002,0.0002,0.0000,0.9998</t>
-  </si>
-  <si>
-    <t>0.9873,0.0003,0.0001,0.0105</t>
-  </si>
-  <si>
-    <t>0.0359,0.0005,0.0009,0.9842</t>
+    <t>1,0,0,1</t>
+  </si>
+  <si>
+    <t>0.9891,0.0011,0.0031,0.0005</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.9924,0.0006,0.0001,0.0036</t>
+  </si>
+  <si>
+    <t>0.0155,0.0006,0.0003,0.9901</t>
   </si>
   <si>
     <t>0.9999,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9995,0.0001,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9994,0.0000,0.0000,0.0004</t>
+    <t>0.9997,0.0000,0.0000,0.0001</t>
   </si>
   <si>
     <t>1.0000,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9960,0.0024,0.0002,0.0007</t>
+    <t>0.9997,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.7600,0.0013,0.2053,0.0003</t>
+  </si>
+  <si>
+    <t>0.0144,0.0010,0.9852,0.0009</t>
+  </si>
+  <si>
+    <t>0.4060,0.0002,0.8014,0.0000</t>
+  </si>
+  <si>
+    <t>0.0010,0.0005,0.9986,0.0001</t>
+  </si>
+  <si>
+    <t>0.9986,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0015,0.9976,0.0011,0.0001</t>
+  </si>
+  <si>
+    <t>0.3255,0.7045,0.0101,0.0008</t>
+  </si>
+  <si>
+    <t>0.0032,0.9963,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.9091,0.0011,0.0510,0.0017</t>
+  </si>
+  <si>
+    <t>0.2431,0.0018,0.7511,0.0005</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.9999,0.0003</t>
+  </si>
+  <si>
+    <t>0.0019,0.0011,0.9945,0.0007</t>
+  </si>
+  <si>
+    <t>0.4022,0.0000,0.8218,0.0000</t>
+  </si>
+  <si>
+    <t>0.0017,0.0000,0.9982,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.9991,0.0012</t>
+  </si>
+  <si>
+    <t>0.0041,0.9954,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.4545,0.0283,0.2303,0.0012</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.9998,0.0026</t>
+  </si>
+  <si>
+    <t>0.0030,0.9149,0.2505,0.0000</t>
+  </si>
+  <si>
+    <t>0.9989,0.0006,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.3876,0.0015,0.4993,0.0002</t>
+  </si>
+  <si>
+    <t>0.9534,0.0512,0.0024,0.0009</t>
+  </si>
+  <si>
+    <t>0.0023,0.9885,0.0377,0.0005</t>
+  </si>
+  <si>
+    <t>0.0020,0.0284,0.9739,0.0013</t>
+  </si>
+  <si>
+    <t>0.0145,0.0027,0.9674,0.0023</t>
+  </si>
+  <si>
+    <t>0.0004,0.0014,0.9984,0.0001</t>
+  </si>
+  <si>
+    <t>0.0149,0.0004,0.9866,0.0005</t>
+  </si>
+  <si>
+    <t>0.0185,0.0186,0.9768,0.0004</t>
+  </si>
+  <si>
+    <t>0.0001,0.9987,0.0043,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9997,0.0001</t>
+  </si>
+  <si>
+    <t>0.0006,0.9688,0.0017,0.7918</t>
+  </si>
+  <si>
+    <t>0.0006,0.9977,0.0008,0.0019</t>
+  </si>
+  <si>
+    <t>0.0002,0.9990,0.0023,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0009,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0169,0.9987,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.0002,0.9981,0.0008</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9997,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.0004,0.9996,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.0005,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.9943,0.0048,0.0003,0.0005</t>
+  </si>
+  <si>
+    <t>0.9987,0.0003,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9542,0.0506,0.0026,0.0004</t>
+  </si>
+  <si>
+    <t>0.0001,0.0013,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0003,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9991,0.0007,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0005,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.8443,0.9864,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.0009,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.0085,0.0259,0.9691,0.0020</t>
+  </si>
+  <si>
+    <t>0.0000,0.9985,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9993,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0035,0.9964,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9788,0.0001,0.0286,0.0000</t>
+  </si>
+  <si>
+    <t>0.1253,0.0006,0.8908,0.0031</t>
+  </si>
+  <si>
+    <t>0.0004,0.0026,0.9989,0.0010</t>
+  </si>
+  <si>
+    <t>0.0000,0.9739,0.9924,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.9672,0.5337,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0132,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9994,0.8138,0.0000</t>
+  </si>
+  <si>
+    <t>0.0267,0.0006,0.0249,0.9557</t>
+  </si>
+  <si>
+    <t>0.0000,0.0068,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0008,0.0000,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0003,0.0006,0.0005,0.9994</t>
+  </si>
+  <si>
+    <t>0.0004,0.0000,0.0003,0.9996</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9984,0.9552,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9974,0.9623,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.2661,0.9882,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.8212,0.9790,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9939,0.9984,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9984,0.4285,0.0000</t>
+  </si>
+  <si>
+    <t>0.9884,0.0152,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0002,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9979,0.0028,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0009,0.0014,0.9990,0.0000</t>
+  </si>
+  <si>
+    <t>0.0561,0.0051,0.9447,0.0002</t>
+  </si>
+  <si>
+    <t>0.9982,0.0001,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0014,0.0002,0.9986,0.0001</t>
+  </si>
+  <si>
+    <t>0.0065,0.9914,0.0015,0.0002</t>
+  </si>
+  <si>
+    <t>0.0008,0.9977,0.0032,0.0001</t>
+  </si>
+  <si>
+    <t>0.0223,0.9812,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.0059,0.9910,0.0042,0.0001</t>
+  </si>
+  <si>
+    <t>0.0008,0.9985,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9996,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.9115,0.1140,0.0017,0.0001</t>
+  </si>
+  <si>
+    <t>0.8768,0.0027,0.0718,0.0007</t>
+  </si>
+  <si>
+    <t>0.9307,0.0139,0.0236,0.0003</t>
+  </si>
+  <si>
+    <t>0.6860,0.0232,0.0697,0.0167</t>
+  </si>
+  <si>
+    <t>0.0459,0.0065,0.9072,0.0020</t>
+  </si>
+  <si>
+    <t>0.0005,0.9242,0.0039,0.8268</t>
+  </si>
+  <si>
+    <t>0.0022,0.9958,0.0013,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9996,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9995,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9989,0.0669,0.0000</t>
+  </si>
+  <si>
+    <t>0.0009,0.9986,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9297,0.0758,0.0038,0.0015</t>
+  </si>
+  <si>
+    <t>0.8760,0.1251,0.0097,0.0052</t>
   </si>
   <si>
     <t>0.9998,0.0001,0.0000,0.0000</t>
   </si>
   <si>
+    <t>0.9991,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9974,0.0008,0.0003,0.0005</t>
+  </si>
+  <si>
+    <t>0.9973,0.0021,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9990,0.0002,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.2631,0.9958,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.8616,0.9992,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0058,0.9989,0.0000</t>
+  </si>
+  <si>
+    <t>0.0010,0.0228,0.9978,0.0000</t>
+  </si>
+  <si>
+    <t>0.9882,0.0002,0.0060,0.0001</t>
+  </si>
+  <si>
+    <t>0.9595,0.0014,0.0217,0.0003</t>
+  </si>
+  <si>
+    <t>0.1205,0.0000,0.9458,0.0001</t>
+  </si>
+  <si>
+    <t>0.9708,0.0010,0.0125,0.0002</t>
+  </si>
+  <si>
+    <t>0.5088,0.0034,0.0001,0.5490</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0000,0.9770,0.9961,0.0000</t>
+  </si>
+  <si>
+    <t>0.4895,0.5407,0.0007,0.0009</t>
+  </si>
+  <si>
+    <t>0.9982,0.0005,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.4345,0.6507,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.5712,0.0001,0.0092,0.2351</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0070,0.9992,0.0003</t>
+  </si>
+  <si>
+    <t>0.9945,0.0000,0.0031,0.0001</t>
+  </si>
+  <si>
+    <t>0.9986,0.0001,0.0000,0.0006</t>
+  </si>
+  <si>
+    <t>0.0556,0.9445,0.0023,0.0005</t>
+  </si>
+  <si>
+    <t>0.9992,0.0002,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9962,0.0018,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0121,0.9822,0.0018,0.0010</t>
+  </si>
+  <si>
+    <t>0.9631,0.0122,0.0020,0.0005</t>
+  </si>
+  <si>
+    <t>0.9994,0.0004,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9980,0.0004,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
     <t>0.9999,0.0000,0.0000,0.0001</t>
   </si>
   <si>
-    <t>0.9553,0.0020,0.0193,0.0003</t>
-  </si>
-  <si>
-    <t>0.0015,0.0002,0.9971,0.0008</t>
-  </si>
-  <si>
-    <t>0.9901,0.0004,0.0035,0.0001</t>
-  </si>
-  <si>
-    <t>0.0007,0.0003,0.9989,0.0001</t>
-  </si>
-  <si>
-    <t>0.9747,0.0003,0.0118,0.0007</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0010,0.9980,0.0014,0.0002</t>
-  </si>
-  <si>
-    <t>0.1403,0.8847,0.0045,0.0005</t>
-  </si>
-  <si>
-    <t>0.0002,0.9997,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.9760,0.0001,0.0177,0.0001</t>
-  </si>
-  <si>
-    <t>0.7933,0.0005,0.2417,0.0002</t>
-  </si>
-  <si>
-    <t>0.0002,0.0003,0.9991,0.0004</t>
-  </si>
-  <si>
-    <t>0.0114,0.0011,0.9788,0.0013</t>
-  </si>
-  <si>
-    <t>0.0358,0.0002,0.9748,0.0003</t>
-  </si>
-  <si>
-    <t>0.0017,0.0002,0.9972,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.0004,0.9996,0.0006</t>
-  </si>
-  <si>
-    <t>0.0074,0.9924,0.0003,0.0014</t>
-  </si>
-  <si>
-    <t>0.9858,0.0021,0.0041,0.0005</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9999,0.0003</t>
-  </si>
-  <si>
-    <t>0.0029,0.9219,0.2807,0.0000</t>
-  </si>
-  <si>
-    <t>0.9925,0.0019,0.0001,0.0025</t>
-  </si>
-  <si>
-    <t>0.9999,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9653,0.0316,0.0035,0.0021</t>
-  </si>
-  <si>
-    <t>0.0046,0.9895,0.0077,0.0003</t>
-  </si>
-  <si>
-    <t>0.0049,0.0964,0.7843,0.0043</t>
-  </si>
-  <si>
-    <t>0.0094,0.0003,0.9920,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.0006,0.9988,0.0001</t>
-  </si>
-  <si>
-    <t>0.7398,0.0012,0.2545,0.0010</t>
-  </si>
-  <si>
-    <t>0.0007,0.3651,0.9860,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.9962,0.0069,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0003,0.9996,0.0001</t>
-  </si>
-  <si>
-    <t>0.0007,0.9173,0.0009,0.9651</t>
-  </si>
-  <si>
-    <t>0.0002,0.9981,0.0010,0.0026</t>
-  </si>
-  <si>
-    <t>0.0001,0.9995,0.0011,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0667,0.9988,0.0000</t>
-  </si>
-  <si>
-    <t>0.0027,0.0008,0.9952,0.0004</t>
-  </si>
-  <si>
-    <t>0.0015,0.0001,0.9984,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.0006,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0068,0.9980,0.0002</t>
-  </si>
-  <si>
-    <t>0.9994,0.0005,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9989,0.0003,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9955,0.0022,0.0006,0.0007</t>
-  </si>
-  <si>
-    <t>0.0000,0.0009,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.9985,0.0008,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9907,0.0113,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9978,0.0018,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9906,0.8842,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.0002,0.9993,0.0000</t>
-  </si>
-  <si>
-    <t>0.0012,0.0022,0.9954,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.9975,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9999,0.0002</t>
-  </si>
-  <si>
-    <t>0.0005,0.9990,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9996,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9895,0.0013,0.0031,0.0001</t>
-  </si>
-  <si>
-    <t>0.9459,0.0029,0.0328,0.0012</t>
-  </si>
-  <si>
-    <t>0.0026,0.0045,0.9944,0.0020</t>
-  </si>
-  <si>
-    <t>0.0000,0.9949,0.9937,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9765,0.8094,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9967,0.0289,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9994,0.7200,0.0000</t>
-  </si>
-  <si>
-    <t>0.0482,0.0019,0.0197,0.9319</t>
-  </si>
-  <si>
-    <t>0.0000,0.0008,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0015,0.9995</t>
-  </si>
-  <si>
-    <t>0.0006,0.0000,0.0046,0.9986</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0000,0.9988,0.0488,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9900,0.9792,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.8611,0.9902,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.8986,0.9826,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9415,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9988,0.2825,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0005,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9983,0.0014,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0000</t>
+    <t>0.9992,0.0002,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9984,0.0001,0.0000,0.0012</t>
+  </si>
+  <si>
+    <t>0.9994,0.0000,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9948,0.0070,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9229,0.1005,0.0013,0.0001</t>
+  </si>
+  <si>
+    <t>0.1045,0.9314,0.0019,0.0001</t>
+  </si>
+  <si>
+    <t>0.0211,0.0236,0.9756,0.0015</t>
+  </si>
+  <si>
+    <t>0.9963,0.0042,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9984,0.0005,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.6395,0.3818,0.0147,0.0018</t>
+  </si>
+  <si>
+    <t>0.0000,0.0081,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.9907,0.0026,0.0012,0.0028</t>
+  </si>
+  <si>
+    <t>0.0000,0.0003,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0045,0.9988,0.0003</t>
+  </si>
+  <si>
+    <t>0.0015,0.0001,0.9985,0.0002</t>
+  </si>
+  <si>
+    <t>0.0020,0.0092,0.9958,0.0002</t>
+  </si>
+  <si>
+    <t>0.0002,0.0003,0.9995,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0007,0.0018,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.0189,0.0009,0.9726,0.0011</t>
+  </si>
+  <si>
+    <t>0.0191,0.0012,0.9834,0.0003</t>
+  </si>
+  <si>
+    <t>0.3174,0.0161,0.6415,0.0012</t>
+  </si>
+  <si>
+    <t>0.0256,0.0075,0.9562,0.0003</t>
+  </si>
+  <si>
+    <t>0.0713,0.0154,0.8735,0.0004</t>
+  </si>
+  <si>
+    <t>0.9709,0.0013,0.0123,0.0002</t>
+  </si>
+  <si>
+    <t>0.9504,0.0038,0.0131,0.0026</t>
+  </si>
+  <si>
+    <t>0.0060,0.0004,0.9936,0.0003</t>
+  </si>
+  <si>
+    <t>0.1583,0.9089,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.0549,0.9653,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9861,0.0187,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0746,0.9419,0.0016,0.0002</t>
+  </si>
+  <si>
+    <t>0.0041,0.9960,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9523,0.0048,0.0192,0.0002</t>
+  </si>
+  <si>
+    <t>0.9954,0.0005,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.9772,0.0026,0.0021,0.0024</t>
+  </si>
+  <si>
+    <t>0.8945,0.0148,0.0343,0.0033</t>
+  </si>
+  <si>
+    <t>0.9485,0.0012,0.0258,0.0006</t>
+  </si>
+  <si>
+    <t>0.0023,0.0013,0.9921,0.0093</t>
+  </si>
+  <si>
+    <t>0.0024,0.0137,0.9900,0.0001</t>
+  </si>
+  <si>
+    <t>0.0020,0.0243,0.9857,0.0008</t>
+  </si>
+  <si>
+    <t>0.0005,0.0005,0.9987,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.8544,0.8573,0.0001</t>
+  </si>
+  <si>
+    <t>0.9983,0.0004,0.0000,0.0003</t>
   </si>
   <si>
     <t>0.9997,0.0002,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9903,0.0131,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9982,0.0028,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0014,0.0005,0.9990,0.0001</t>
-  </si>
-  <si>
-    <t>0.0852,0.0056,0.9102,0.0002</t>
-  </si>
-  <si>
-    <t>0.9848,0.0010,0.0038,0.0003</t>
-  </si>
-  <si>
-    <t>0.1127,0.0002,0.9415,0.0001</t>
-  </si>
-  <si>
-    <t>0.0008,0.9979,0.0007,0.0005</t>
-  </si>
-  <si>
-    <t>0.0014,0.9964,0.0045,0.0001</t>
-  </si>
-  <si>
-    <t>0.0045,0.9941,0.0014,0.0001</t>
-  </si>
-  <si>
-    <t>0.0013,0.9971,0.0027,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9997,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9990,0.0011,0.0000</t>
-  </si>
-  <si>
-    <t>0.6204,0.4768,0.0036,0.0002</t>
-  </si>
-  <si>
-    <t>0.2136,0.0127,0.6325,0.0032</t>
-  </si>
-  <si>
-    <t>0.8159,0.1278,0.0080,0.0007</t>
-  </si>
-  <si>
-    <t>0.1880,0.0213,0.5094,0.0047</t>
-  </si>
-  <si>
-    <t>0.5695,0.0008,0.4380,0.0010</t>
-  </si>
-  <si>
-    <t>0.0011,0.2274,0.0011,0.9771</t>
-  </si>
-  <si>
-    <t>0.0011,0.9977,0.0009,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9989,0.0012,0.0015</t>
-  </si>
-  <si>
-    <t>0.0001,0.9991,0.0015,0.0004</t>
-  </si>
-  <si>
-    <t>0.0000,0.9874,0.9816,0.0000</t>
-  </si>
-  <si>
-    <t>0.7339,0.3086,0.0028,0.0008</t>
-  </si>
-  <si>
-    <t>0.8777,0.1439,0.0036,0.0013</t>
-  </si>
-  <si>
-    <t>0.9994,0.0003,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9977,0.0005,0.0001,0.0009</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9983,0.0010,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9978,0.0007,0.0003,0.0006</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.6508,0.9911,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9415,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0164,0.9993,0.0000</t>
-  </si>
-  <si>
-    <t>0.0064,0.0056,0.9905,0.0002</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.8922,0.0004,0.0555,0.0011</t>
-  </si>
-  <si>
-    <t>0.3631,0.0001,0.7984,0.0001</t>
-  </si>
-  <si>
-    <t>0.9852,0.0002,0.0073,0.0001</t>
-  </si>
-  <si>
-    <t>0.5556,0.0009,0.0001,0.6701</t>
-  </si>
-  <si>
-    <t>0.0000,0.0004,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0014,0.0001,0.0000,0.9996</t>
-  </si>
-  <si>
-    <t>0.0000,0.9992,0.9620,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0237,0.9730,0.0008,0.0030</t>
-  </si>
-  <si>
-    <t>0.9995,0.0000,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.0309,0.9656,0.0041,0.0002</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.4176,0.0000,0.0003,0.7611</t>
-  </si>
-  <si>
-    <t>0.9989,0.0000,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0120,0.9992,0.0002</t>
-  </si>
-  <si>
-    <t>0.9987,0.0000,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9985,0.0003,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.0568,0.2666,0.2311,0.0020</t>
-  </si>
-  <si>
-    <t>0.9941,0.0048,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9933,0.0014,0.0007,0.0003</t>
-  </si>
-  <si>
-    <t>0.1347,0.7975,0.0024,0.0129</t>
-  </si>
-  <si>
-    <t>0.9410,0.0430,0.0020,0.0019</t>
-  </si>
-  <si>
-    <t>0.9911,0.0073,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9969,0.0009,0.0003,0.0007</t>
-  </si>
-  <si>
-    <t>0.9989,0.0003,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9976,0.0005,0.0004,0.0004</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9972,0.0035,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.8698,0.1427,0.0054,0.0002</t>
-  </si>
-  <si>
-    <t>0.1080,0.9325,0.0017,0.0001</t>
-  </si>
-  <si>
-    <t>0.7549,0.2702,0.0101,0.0022</t>
-  </si>
-  <si>
-    <t>0.9971,0.0019,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9993,0.0002,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9843,0.0089,0.0026,0.0011</t>
-  </si>
-  <si>
-    <t>0.0000,0.0027,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.9544,0.0161,0.0210,0.0074</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0030,0.9993,0.0001</t>
-  </si>
-  <si>
-    <t>0.0017,0.0001,0.9984,0.0002</t>
-  </si>
-  <si>
-    <t>0.0006,0.0150,0.9960,0.0003</t>
-  </si>
-  <si>
-    <t>0.0005,0.0008,0.9992,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.0001,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0009,0.0027,0.9991,0.0000</t>
-  </si>
-  <si>
-    <t>0.0029,0.0002,0.9934,0.0014</t>
-  </si>
-  <si>
-    <t>0.0014,0.0003,0.9984,0.0001</t>
-  </si>
-  <si>
-    <t>0.0167,0.0085,0.9509,0.0028</t>
-  </si>
-  <si>
-    <t>0.0010,0.0022,0.9980,0.0001</t>
-  </si>
-  <si>
-    <t>0.0147,0.1717,0.7267,0.0007</t>
-  </si>
-  <si>
-    <t>0.2393,0.0160,0.6009,0.0007</t>
-  </si>
-  <si>
-    <t>0.9441,0.0236,0.0041,0.0017</t>
-  </si>
-  <si>
-    <t>0.1359,0.0009,0.9140,0.0009</t>
-  </si>
-  <si>
-    <t>0.0705,0.9505,0.0019,0.0002</t>
-  </si>
-  <si>
-    <t>0.0067,0.9934,0.0010,0.0001</t>
-  </si>
-  <si>
-    <t>0.9873,0.0195,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.2301,0.8379,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.0696,0.9573,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9841,0.0034,0.0023,0.0002</t>
-  </si>
-  <si>
-    <t>0.9944,0.0001,0.0018,0.0000</t>
-  </si>
-  <si>
-    <t>0.9555,0.0051,0.0093,0.0035</t>
-  </si>
-  <si>
-    <t>0.9335,0.0074,0.0165,0.0012</t>
-  </si>
-  <si>
-    <t>0.7405,0.0016,0.1382,0.0040</t>
-  </si>
-  <si>
-    <t>0.0025,0.0005,0.9944,0.0054</t>
-  </si>
-  <si>
-    <t>0.0023,0.0053,0.9882,0.0018</t>
-  </si>
-  <si>
-    <t>0.0004,0.0078,0.9961,0.0004</t>
-  </si>
-  <si>
-    <t>0.0003,0.0004,0.9992,0.0001</t>
-  </si>
-  <si>
-    <t>0.0028,0.6514,0.7402,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9990,0.0006,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9924,0.0045,0.0012,0.0005</t>
-  </si>
-  <si>
-    <t>0.9994,0.0002,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9991,0.0001,0.0000,0.0004</t>
-  </si>
-  <si>
-    <t>0.9995,0.0000,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.0094,0.0092,0.9775,0.0051</t>
-  </si>
-  <si>
-    <t>0.0732,0.1129,0.5861,0.0029</t>
-  </si>
-  <si>
-    <t>0.9454,0.0008,0.0211,0.0015</t>
-  </si>
-  <si>
-    <t>0.0813,0.0019,0.9333,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0006,0.9996,0.0004</t>
-  </si>
-  <si>
-    <t>0.0410,0.1314,0.7332,0.0002</t>
-  </si>
-  <si>
-    <t>0.0005,0.0009,0.9990,0.0001</t>
-  </si>
-  <si>
-    <t>0.0392,0.0021,0.9584,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.0004,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0015,0.0011,0.9944,0.0005</t>
-  </si>
-  <si>
-    <t>0.0014,0.0017,0.9949,0.0022</t>
-  </si>
-  <si>
-    <t>0.7457,0.0004,0.2515,0.0005</t>
-  </si>
-  <si>
-    <t>0.4930,0.0001,0.6062,0.0004</t>
-  </si>
-  <si>
-    <t>0.9893,0.0008,0.0035,0.0002</t>
-  </si>
-  <si>
-    <t>0.9993,0.0004,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9991,0.0005,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9982,0.0007,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9928,0.0106,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0035,0.9981,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0021,0.9993,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.0013,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0038,0.0050,0.9890,0.0009</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.1752,0.0012,0.6670,0.0237</t>
-  </si>
-  <si>
-    <t>0.0020,0.0053,0.9956,0.0004</t>
-  </si>
-  <si>
-    <t>0.0012,0.0039,0.9921,0.0013</t>
-  </si>
-  <si>
-    <t>0.3195,0.0004,0.0020,0.7146</t>
-  </si>
-  <si>
-    <t>0.0075,0.0531,0.0001,0.9933</t>
-  </si>
-  <si>
-    <t>0.0030,0.0001,0.0005,0.9982</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.9912,0.0008,0.0002,0.0042</t>
+    <t>0.9967,0.0011,0.0005,0.0006</t>
+  </si>
+  <si>
+    <t>0.9990,0.0005,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9989,0.0003,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.0002,0.0777,0.9982,0.0001</t>
+  </si>
+  <si>
+    <t>0.0410,0.0119,0.8884,0.0139</t>
+  </si>
+  <si>
+    <t>0.9698,0.0004,0.0127,0.0004</t>
+  </si>
+  <si>
+    <t>0.0008,0.0002,0.9982,0.0003</t>
+  </si>
+  <si>
+    <t>0.0002,0.0009,0.9995,0.0002</t>
+  </si>
+  <si>
+    <t>0.0008,0.2955,0.9692,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.0006,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0016,0.0008,0.9970,0.0001</t>
+  </si>
+  <si>
+    <t>0.0010,0.0021,0.9956,0.0003</t>
+  </si>
+  <si>
+    <t>0.0026,0.0057,0.9931,0.0005</t>
+  </si>
+  <si>
+    <t>0.8365,0.0039,0.0809,0.0031</t>
+  </si>
+  <si>
+    <t>0.5839,0.0002,0.4316,0.0007</t>
+  </si>
+  <si>
+    <t>0.9911,0.0008,0.0027,0.0004</t>
+  </si>
+  <si>
+    <t>0.9993,0.0004,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9985,0.0010,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9969,0.0046,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9988,0.0003,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.0010,0.0020,0.9974,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0019,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0059,0.9975,0.0006</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0133,0.0013,0.9827,0.0017</t>
+  </si>
+  <si>
+    <t>0.0014,0.0012,0.9959,0.0005</t>
+  </si>
+  <si>
+    <t>0.0012,0.0020,0.9887,0.0046</t>
+  </si>
+  <si>
+    <t>0.9840,0.0003,0.0003,0.0088</t>
+  </si>
+  <si>
+    <t>0.0040,0.0834,0.0000,0.9927</t>
+  </si>
+  <si>
+    <t>0.0002,0.0002,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.9975,0.0004,0.0002,0.0008</t>
   </si>
 </sst>
 </file>
@@ -1890,7 +1869,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1904,7 +1883,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1918,7 +1897,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1932,7 +1911,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1946,7 +1925,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1960,7 +1939,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1988,7 +1967,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2002,7 +1981,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2016,7 +1995,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2030,7 +2009,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2044,7 +2023,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2058,7 +2037,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2072,7 +2051,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2083,10 +2062,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2100,7 +2079,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2114,7 +2093,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2128,7 +2107,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2142,7 +2121,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2156,7 +2135,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2170,7 +2149,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2184,7 +2163,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2198,7 +2177,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2209,10 +2188,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2226,7 +2205,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2240,7 +2219,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2254,7 +2233,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2268,7 +2247,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2282,7 +2261,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2296,7 +2275,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2307,10 +2286,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2324,7 +2303,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2338,7 +2317,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2352,7 +2331,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2363,10 +2342,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2380,7 +2359,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2394,7 +2373,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2408,7 +2387,7 @@
         <v>261</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2422,7 +2401,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2436,7 +2415,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2447,10 +2426,10 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2464,7 +2443,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2478,7 +2457,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2492,7 +2471,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2503,10 +2482,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2520,7 +2499,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2534,7 +2513,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2548,7 +2527,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2562,7 +2541,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2576,7 +2555,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2590,7 +2569,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2604,7 +2583,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2618,7 +2597,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2632,7 +2611,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2646,7 +2625,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2660,7 +2639,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2674,7 +2653,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2688,7 +2667,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2702,7 +2681,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2716,7 +2695,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2730,7 +2709,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2744,7 +2723,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2758,7 +2737,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2772,7 +2751,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2786,7 +2765,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2800,7 +2779,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2814,7 +2793,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2828,7 +2807,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2842,7 +2821,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2853,10 +2832,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2870,7 +2849,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2884,7 +2863,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2898,7 +2877,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2912,7 +2891,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2926,7 +2905,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2940,7 +2919,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2954,7 +2933,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2968,7 +2947,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2982,7 +2961,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2996,7 +2975,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3010,7 +2989,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3021,10 +3000,10 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3038,7 +3017,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3049,10 +3028,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3066,7 +3045,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3080,7 +3059,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3094,7 +3073,7 @@
         <v>262</v>
       </c>
       <c r="D88" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3108,7 +3087,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3122,7 +3101,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>351</v>
+        <v>271</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3136,7 +3115,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3150,7 +3129,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3164,7 +3143,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>269</v>
+        <v>351</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3178,7 +3157,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>269</v>
+        <v>351</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3192,7 +3171,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3206,7 +3185,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3220,7 +3199,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3234,7 +3213,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3248,7 +3227,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3262,7 +3241,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3276,7 +3255,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3290,7 +3269,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3304,7 +3283,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3318,7 +3297,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3332,7 +3311,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3346,7 +3325,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3360,7 +3339,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3374,7 +3353,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3388,7 +3367,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3402,7 +3381,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3416,7 +3395,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3430,7 +3409,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3444,7 +3423,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3458,7 +3437,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3472,7 +3451,7 @@
         <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3483,10 +3462,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3500,7 +3479,7 @@
         <v>259</v>
       </c>
       <c r="D117" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3511,10 +3490,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3525,10 +3504,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3539,10 +3518,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="D120" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3556,7 +3535,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3570,7 +3549,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3584,7 +3563,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3595,10 +3574,10 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D124" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3612,7 +3591,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3626,7 +3605,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3640,7 +3619,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3654,7 +3633,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3668,7 +3647,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3682,7 +3661,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3696,7 +3675,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3710,7 +3689,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>382</v>
+        <v>271</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3724,7 +3703,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3738,7 +3717,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3752,7 +3731,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>385</v>
+        <v>271</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3763,10 +3742,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D136" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3780,7 +3759,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3794,7 +3773,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3808,7 +3787,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3822,7 +3801,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3836,7 +3815,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3850,7 +3829,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3864,7 +3843,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3875,10 +3854,10 @@
         <v>260</v>
       </c>
       <c r="C144" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="D144" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3892,7 +3871,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3906,7 +3885,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3920,7 +3899,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3934,7 +3913,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3948,7 +3927,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>399</v>
+        <v>271</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3962,7 +3941,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3976,7 +3955,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3990,7 +3969,7 @@
         <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4004,7 +3983,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4015,10 +3994,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4032,7 +4011,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4046,7 +4025,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4060,7 +4039,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4074,7 +4053,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4085,10 +4064,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4102,7 +4081,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4116,7 +4095,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4130,7 +4109,7 @@
         <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4144,7 +4123,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4158,7 +4137,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4172,7 +4151,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4186,7 +4165,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>382</v>
+        <v>412</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4200,7 +4179,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>416</v>
+        <v>351</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4214,7 +4193,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4228,7 +4207,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>418</v>
+        <v>354</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4242,7 +4221,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4256,7 +4235,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4270,7 +4249,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4284,7 +4263,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4298,7 +4277,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4312,7 +4291,7 @@
         <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4323,10 +4302,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4340,7 +4319,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4354,7 +4333,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4368,7 +4347,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>353</v>
+        <v>401</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4382,7 +4361,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4396,7 +4375,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4410,7 +4389,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4424,7 +4403,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4438,7 +4417,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4452,7 +4431,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4466,7 +4445,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4480,7 +4459,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4494,7 +4473,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4508,7 +4487,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4522,7 +4501,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4536,7 +4515,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4550,7 +4529,7 @@
         <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4564,7 +4543,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4578,7 +4557,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4589,10 +4568,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4606,7 +4585,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4620,7 +4599,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4634,7 +4613,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4648,7 +4627,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4662,7 +4641,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4676,7 +4655,7 @@
         <v>262</v>
       </c>
       <c r="D201" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4690,7 +4669,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4704,7 +4683,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4718,7 +4697,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4732,7 +4711,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4746,7 +4725,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4760,7 +4739,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4774,7 +4753,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4788,7 +4767,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4802,7 +4781,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4816,7 +4795,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4830,7 +4809,7 @@
         <v>263</v>
       </c>
       <c r="D212" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4844,7 +4823,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>460</v>
+        <v>272</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4858,7 +4837,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4872,7 +4851,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4886,7 +4865,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>399</v>
+        <v>457</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4900,7 +4879,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4914,7 +4893,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4928,7 +4907,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4942,7 +4921,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>465</v>
+        <v>413</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4956,7 +4935,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4970,7 +4949,7 @@
         <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4984,7 +4963,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4998,7 +4977,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5012,7 +4991,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5026,7 +5005,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5040,7 +5019,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5054,7 +5033,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5068,7 +5047,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>474</v>
+        <v>327</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5082,7 +5061,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5096,7 +5075,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5110,7 +5089,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5121,10 +5100,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5138,7 +5117,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5152,7 +5131,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>480</v>
+        <v>410</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5166,7 +5145,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>353</v>
+        <v>474</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5180,7 +5159,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5194,7 +5173,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5208,7 +5187,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>482</v>
+        <v>271</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5222,7 +5201,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>354</v>
+        <v>378</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5236,7 +5215,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>483</v>
+        <v>476</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5250,7 +5229,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>270</v>
+        <v>477</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5264,7 +5243,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>484</v>
+        <v>478</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5278,7 +5257,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5292,7 +5271,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5306,7 +5285,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>487</v>
+        <v>481</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5320,7 +5299,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5334,7 +5313,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>489</v>
+        <v>483</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5348,7 +5327,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5362,7 +5341,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5373,10 +5352,10 @@
         <v>259</v>
       </c>
       <c r="C251" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>492</v>
+        <v>486</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5390,7 +5369,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>493</v>
+        <v>487</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5404,7 +5383,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>494</v>
+        <v>488</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5418,7 +5397,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>495</v>
+        <v>392</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5432,7 +5411,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>495</v>
+        <v>392</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5446,7 +5425,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>496</v>
+        <v>489</v>
       </c>
     </row>
   </sheetData>
